--- a/runs/RELX/2026-10-14/bear/scratch/gs_5ym_beta/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/gs_5ym_beta/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2567.232139688373</v>
+        <v>2596.032303810942</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.068801</v>
+        <v>0.0657746</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.06561123967456001</v>
+        <v>0.06297276362656</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>12677.36884968541</v>
+        <v>12756.79188342264</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>77852.60149583593</v>
+        <v>83030.26510038839</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>58489.58804649438</v>
+        <v>63079.29181440578</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>71166.95689617978</v>
+        <v>75836.08369782842</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>64169.95689617978</v>
+        <v>68839.08369782842</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>64331.07574802321</v>
+        <v>69089.1320954455</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>36.89227318035721</v>
+        <v>39.62090024800002</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3689.227318035722</v>
+        <v>3962.090024800002</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>0.3313703782</v>
+        <v>0.4298412215</v>
       </c>
     </row>
   </sheetData>
